--- a/tsrtsV5_final_reduced_com_epg/urls_geral.xlsx
+++ b/tsrtsV5_final_reduced_com_epg/urls_geral.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="urls" sheetId="1" state="visible" r:id="rId2"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t xml:space="preserve">urls_geral</t>
   </si>
@@ -30,9 +30,6 @@
     <t xml:space="preserve">https://i.mjh.nz/all/raw.m3u8</t>
   </si>
   <si>
-    <t xml:space="preserve">https://i.mjh.nz/PBS/all.m3u8</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://i.mjh.nz/Plex/all.m3u8</t>
   </si>
   <si>
@@ -63,6 +60,9 @@
     <t xml:space="preserve">Bis</t>
   </si>
   <si>
+    <t xml:space="preserve">Blues</t>
+  </si>
+  <si>
     <t xml:space="preserve">BMTV</t>
   </si>
   <si>
@@ -141,6 +141,9 @@
     <t xml:space="preserve">OurVinyl</t>
   </si>
   <si>
+    <t xml:space="preserve">Our Vinyl</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pluto TV Fireplace</t>
   </si>
   <si>
@@ -157,6 +160,9 @@
   </si>
   <si>
     <t xml:space="preserve">RockZone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rock Zone</t>
   </si>
   <si>
     <t xml:space="preserve">Rock TV</t>
@@ -393,8 +399,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="8.48046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:A1048576"/>
+  <sheetFormatPr defaultColWidth="8.49609375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="128.34"/>
   </cols>
@@ -434,11 +440,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>7</v>
-      </c>
-    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -455,242 +457,257 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A47"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:A50"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -710,44 +727,44 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="78.02"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
